--- a/bancos/manual/desc_fontes_de_recursos.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos.xlsx
@@ -1,41 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m753205\Desktop\99 TABELAS APOIO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_50E8B19B325462AB430540D226A1CE6240D7173E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{918EBDB3-B38F-4D91-B10C-BC2CD208FFA2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19350" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Plan1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$100</definedName>
-    <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Plan1!$A$1:$C$100</definedName>
+    <definedName name="LOCAL_MYSQL_DATE_FORMAT">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -549,7 +527,7 @@
     <t>TRANSFERÊNCIAS DO SUS PARA A VIGILÂNCIA EM SAÚDE</t>
   </si>
   <si>
-    <t>RECURSOS TRANSFERIDOS PARA FINANCIAMENTO DE AÇÕES DE VIGILÂNCIA EM SAÚDE, CONFORME DISPÕE A PORTARIA N° 204/GM, DE 29/01/2007, DO MINISTÉRIO DA SAÚDE. </t>
+    <t xml:space="preserve">RECURSOS TRANSFERIDOS PARA FINANCIAMENTO DE AÇÕES DE VIGILÂNCIA EM SAÚDE, CONFORME DISPÕE A PORTARIA N° 204/GM, DE 29/01/2007, DO MINISTÉRIO DA SAÚDE. </t>
   </si>
   <si>
     <t>TRANSFERÊNCIAS DO SUS PARA A ASSISTÊNCIA FARMACÊUTICA</t>
@@ -639,8 +617,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,7 +632,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -664,7 +642,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -676,41 +661,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -737,85 +733,85 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -824,1569 +820,1279 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="61" style="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="8.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1">
+      <c r="C42" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="1">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+      <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+      <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+      <c r="A55" s="3">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="1">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="1">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+      <c r="A57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="1">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+      <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="1">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+      <c r="A59" s="3">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="1">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+      <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="1">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+      <c r="A61" s="3">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="1">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+      <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="1">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+      <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+      <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="1">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+      <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="1">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+      <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="1">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+      <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="1">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+      <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="1">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+      <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="1">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+      <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="1">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="1">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+      <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="1">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+      <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="1">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="1">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="1">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+      <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="1">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+      <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="1">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+      <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="1">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+      <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="1">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+      <c r="A81" s="3">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="1">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+      <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="1">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+      <c r="A83" s="3">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="1">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+      <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="1">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+      <c r="A85" s="3">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="1">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+      <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="1">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+      <c r="A87" s="3">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="1">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+      <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="1">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+      <c r="A89" s="3">
         <v>88</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="1">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+      <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="1">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+      <c r="A91" s="3">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="1">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+      <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="1">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+      <c r="A93" s="3">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="1">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="1">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="3">
         <v>94</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="1">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+      <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="1">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+      <c r="A97" s="3">
         <v>96</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="1">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+      <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="1">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+      <c r="A99" s="3">
         <v>98</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="1">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+      <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="2" t="s">
         <v>197</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
-    <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
-    <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6f4338ef-addb-4c87-aefe-1895241b335f" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="917d32f3-4fa4-4f5b-a8d0-62dbd3d265b9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{98708050-f001-4dcd-9fe1-c60e835c33fc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <UserInfo>
-        <DisplayName>Sofia Chacon Furletti (SEPLAG)</DisplayName>
-        <AccountId>70</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Rodolfo Pinhón Bechtlufft (SEPLAG)</DisplayName>
-        <AccountId>38</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Carlos Henrique de Oliveira Brochado (SEPLAG)</DisplayName>
-        <AccountId>49</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Carolina Fonseca Moreira (SEPLAG)</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52695D42-7905-4355-AFA3-D66DFF9609E9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC3FA630-D18C-4B56-A359-9CD6CF90D85A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741C4EED-4E68-4D13-8A53-EE95607C61BA}"/>
 </file>
--- a/bancos/manual/desc_fontes_de_recursos.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos.xlsx
@@ -994,7 +994,7 @@
     <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C42" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="3">
         <v>50</v>
       </c>

--- a/bancos/manual/desc_fontes_de_recursos.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos.xlsx
@@ -994,7 +994,7 @@
     <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C42" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3">
         <v>50</v>
       </c>

--- a/bancos/manual/desc_fontes_de_recursos.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos.xlsx
@@ -1,19 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19350" windowHeight="7965"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Plan1"/>
+    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Plan1!$A$1:$C$100</definedName>
-    <definedName name="LOCAL_MYSQL_DATE_FORMAT">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$100</definedName>
+    <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -488,12 +509,6 @@
     <t xml:space="preserve">CONTRIBUIÇÃO SOBRE A TOTALIDADE DA REMUNERAÇÃO DOS MILITARES ATIVOS, INATIVOS E PENSIONISTAS, DESTINADA AO CUSTEIO DAS PENSÕES E INATIVIDADE DOS MILITARES – LEI 13.954/2019 </t>
   </si>
   <si>
-    <t>CONTRIBUIÇÃO PATRONAL PARA O FUNPREV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECURSOS ADVINDOS DE CONTRIBUIÇÃO PATRONAL, VINCULADOS AO PAGAMENTO DOS BENEFÍCIOS CONCEDIDOS NA FORMA DO ART. 3º DA LEI COMPLEMENTAR Nº 132/2014. </t>
-  </si>
-  <si>
     <t>RECURSOS DO ACORDO DE REPACTUAÇÃO DO RIO DOCE</t>
   </si>
   <si>
@@ -527,7 +542,7 @@
     <t>TRANSFERÊNCIAS DO SUS PARA A VIGILÂNCIA EM SAÚDE</t>
   </si>
   <si>
-    <t xml:space="preserve">RECURSOS TRANSFERIDOS PARA FINANCIAMENTO DE AÇÕES DE VIGILÂNCIA EM SAÚDE, CONFORME DISPÕE A PORTARIA N° 204/GM, DE 29/01/2007, DO MINISTÉRIO DA SAÚDE. </t>
+    <t>RECURSOS TRANSFERIDOS PARA FINANCIAMENTO DE AÇÕES DE VIGILÂNCIA EM SAÚDE, CONFORME DISPÕE A PORTARIA N° 204/GM, DE 29/01/2007, DO MINISTÉRIO DA SAÚDE. </t>
   </si>
   <si>
     <t>TRANSFERÊNCIAS DO SUS PARA A ASSISTÊNCIA FARMACÊUTICA</t>
@@ -612,13 +627,18 @@
   </si>
   <si>
     <t>RECURSOS PREVISTOS NO ART. 5º, INCISO I, A, DA LEI COMPLEMENTAR Nº 173/2020, DESTINADOS A AÇÕES DE ENFRENTAMENTO À COVID-19, A SEREM APLICADOS EM AÇÕES DE SAÚDE E ASSISTÊNCIA SOCIAL.</t>
+  </si>
+  <si>
+    <t>RECURSOS DECORRENTES DA CONVERSÃO DE MULTAS AMBIENTAIS</t>
+  </si>
+  <si>
+    <t>RECURSOS DECORRENTES DA CONVERSÃO DE MULTAS AMBIENTAIS, A QUE SE REFEREM O § 6° DO ART. 16 DA LEI Nº 7.772, DE 8 DE SETEMBRO DE 1980, O § 6º DO ART. 20 DA LEI Nº 14.181, DE 17 DE JANEIRO DE 2002, E O ART. 106-A DA LEI Nº 20.922, DE 16 DE OUTUBRO DE 2013.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -632,6 +652,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -642,14 +663,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -661,52 +675,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -733,85 +736,85 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -820,1279 +823,1601 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
-            </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="8.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="61" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="3">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="3">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="3">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="3">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="3">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="3">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="3">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="3">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="3">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="3">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="3">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="3">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="3">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="3">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="3">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="3">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="3">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="3">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="3">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="3">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="3">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName>Sofia Chacon Furletti (SEPLAG)</DisplayName>
+        <AccountId>70</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rodolfo Pinhón Bechtlufft (SEPLAG)</DisplayName>
+        <AccountId>38</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Carlos Henrique de Oliveira Brochado (SEPLAG)</DisplayName>
+        <AccountId>49</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Carolina Fonseca Moreira (SEPLAG)</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
+    <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6f4338ef-addb-4c87-aefe-1895241b335f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="917d32f3-4fa4-4f5b-a8d0-62dbd3d265b9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{98708050-f001-4dcd-9fe1-c60e835c33fc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741C4EED-4E68-4D13-8A53-EE95607C61BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52695D42-7905-4355-AFA3-D66DFF9609E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9398F535-E0C5-40FC-A458-15A5F4068865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>